--- a/堆存计划测试数据20260508补充/箱区功能.xlsx
+++ b/堆存计划测试数据20260508补充/箱区功能.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\container_terminal\stacking\堆存计划测试数据20260508补充\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557A40BF-1F78-4325-8876-B8F4DF5B99F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="21094" windowHeight="9805"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$159</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="89">
   <si>
     <t>area_no</t>
   </si>
@@ -302,14 +308,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,345 +318,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -664,251 +340,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -917,89 +351,158 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1010,7 +513,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1038,154 +541,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1435,20 +824,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C160"/>
-  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C159"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.7657657657658" customWidth="1"/>
-    <col min="3" max="3" width="16.9009009009009" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1459,7 +848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>19</v>
       </c>
@@ -1470,7 +859,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1481,7 +870,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1492,7 +881,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1503,7 +892,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1514,7 +903,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1525,7 +914,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1536,7 +925,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>28</v>
       </c>
@@ -1547,7 +936,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>29</v>
       </c>
@@ -1558,7 +947,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1569,7 +958,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1580,7 +969,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1591,7 +980,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1602,7 +991,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1613,7 +1002,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1624,7 +1013,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>38</v>
       </c>
@@ -1635,7 +1024,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>39</v>
       </c>
@@ -1646,7 +1035,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -1657,7 +1046,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1668,7 +1057,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1679,7 +1068,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -1690,7 +1079,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -1701,7 +1090,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -1712,7 +1101,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -1723,7 +1112,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -1734,7 +1123,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>49</v>
       </c>
@@ -1745,7 +1134,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -1756,7 +1145,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -1767,7 +1156,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -1778,7 +1167,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -1789,7 +1178,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -1800,7 +1189,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -1811,7 +1200,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>30</v>
       </c>
@@ -1822,7 +1211,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -1833,7 +1222,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>32</v>
       </c>
@@ -1844,7 +1233,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -1855,7 +1244,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>59</v>
       </c>
@@ -1866,7 +1255,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>34</v>
       </c>
@@ -1877,7 +1266,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>35</v>
       </c>
@@ -1888,7 +1277,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>36</v>
       </c>
@@ -1899,7 +1288,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -1910,7 +1299,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1310,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>39</v>
       </c>
@@ -1932,7 +1321,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>40</v>
       </c>
@@ -1943,7 +1332,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>41</v>
       </c>
@@ -1954,7 +1343,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1965,7 +1354,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>43</v>
       </c>
@@ -1976,7 +1365,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>69</v>
       </c>
@@ -1987,7 +1376,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1387,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>45</v>
       </c>
@@ -2009,7 +1398,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>46</v>
       </c>
@@ -2020,7 +1409,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>47</v>
       </c>
@@ -2031,7 +1420,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -2042,7 +1431,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -2053,7 +1442,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>50</v>
       </c>
@@ -2064,7 +1453,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>51</v>
       </c>
@@ -2075,7 +1464,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>79</v>
       </c>
@@ -2086,7 +1475,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>52</v>
       </c>
@@ -2097,7 +1486,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>53</v>
       </c>
@@ -2108,7 +1497,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>54</v>
       </c>
@@ -2119,7 +1508,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -2130,7 +1519,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>89</v>
       </c>
@@ -2141,7 +1530,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>56</v>
       </c>
@@ -2152,7 +1541,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>57</v>
       </c>
@@ -2163,7 +1552,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>58</v>
       </c>
@@ -2174,7 +1563,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>59</v>
       </c>
@@ -2185,7 +1574,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>60</v>
       </c>
@@ -2196,7 +1585,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>61</v>
       </c>
@@ -2207,7 +1596,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>62</v>
       </c>
@@ -2218,7 +1607,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>63</v>
       </c>
@@ -2229,7 +1618,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>64</v>
       </c>
@@ -2240,7 +1629,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>66</v>
       </c>
@@ -2251,7 +1640,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>67</v>
       </c>
@@ -2262,7 +1651,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>68</v>
       </c>
@@ -2273,7 +1662,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>69</v>
       </c>
@@ -2284,7 +1673,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>70</v>
       </c>
@@ -2295,7 +1684,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>71</v>
       </c>
@@ -2306,7 +1695,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>72</v>
       </c>
@@ -2317,7 +1706,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>73</v>
       </c>
@@ -2328,7 +1717,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>74</v>
       </c>
@@ -2339,7 +1728,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>75</v>
       </c>
@@ -2350,7 +1739,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>76</v>
       </c>
@@ -2361,7 +1750,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>77</v>
       </c>
@@ -2372,7 +1761,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>78</v>
       </c>
@@ -2383,7 +1772,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>10</v>
       </c>
@@ -2394,7 +1783,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>11</v>
       </c>
@@ -2405,7 +1794,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>12</v>
       </c>
@@ -2416,7 +1805,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>20</v>
       </c>
@@ -2427,7 +1816,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>21</v>
       </c>
@@ -2438,7 +1827,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>30</v>
       </c>
@@ -2449,7 +1838,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>31</v>
       </c>
@@ -2460,7 +1849,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>40</v>
       </c>
@@ -2471,7 +1860,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>41</v>
       </c>
@@ -2482,7 +1871,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>51</v>
       </c>
@@ -2493,7 +1882,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>60</v>
       </c>
@@ -2504,7 +1893,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>61</v>
       </c>
@@ -2515,7 +1904,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>70</v>
       </c>
@@ -2526,7 +1915,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>71</v>
       </c>
@@ -2537,7 +1926,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>80</v>
       </c>
@@ -2548,7 +1937,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>81</v>
       </c>
@@ -2559,7 +1948,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>90</v>
       </c>
@@ -2570,7 +1959,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>80</v>
       </c>
@@ -2581,7 +1970,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>13</v>
       </c>
@@ -2592,7 +1981,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>14</v>
       </c>
@@ -2603,7 +1992,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>15</v>
       </c>
@@ -2614,7 +2003,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>16</v>
       </c>
@@ -2625,7 +2014,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>17</v>
       </c>
@@ -2636,7 +2025,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>22</v>
       </c>
@@ -2647,7 +2036,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>23</v>
       </c>
@@ -2658,7 +2047,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>24</v>
       </c>
@@ -2669,7 +2058,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>25</v>
       </c>
@@ -2680,7 +2069,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>26</v>
       </c>
@@ -2691,7 +2080,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>27</v>
       </c>
@@ -2702,7 +2091,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>32</v>
       </c>
@@ -2713,7 +2102,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>33</v>
       </c>
@@ -2724,7 +2113,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>37</v>
       </c>
@@ -2735,7 +2124,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>42</v>
       </c>
@@ -2746,7 +2135,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>43</v>
       </c>
@@ -2757,7 +2146,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>44</v>
       </c>
@@ -2768,7 +2157,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>45</v>
       </c>
@@ -2779,7 +2168,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>46</v>
       </c>
@@ -2790,7 +2179,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>47</v>
       </c>
@@ -2801,7 +2190,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>52</v>
       </c>
@@ -2812,7 +2201,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>53</v>
       </c>
@@ -2823,7 +2212,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>54</v>
       </c>
@@ -2834,7 +2223,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>55</v>
       </c>
@@ -2845,7 +2234,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>57</v>
       </c>
@@ -2856,7 +2245,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>62</v>
       </c>
@@ -2867,7 +2256,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>63</v>
       </c>
@@ -2878,7 +2267,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>64</v>
       </c>
@@ -2889,7 +2278,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>65</v>
       </c>
@@ -2900,7 +2289,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>66</v>
       </c>
@@ -2911,7 +2300,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>67</v>
       </c>
@@ -2922,7 +2311,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>72</v>
       </c>
@@ -2933,7 +2322,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>73</v>
       </c>
@@ -2944,7 +2333,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>74</v>
       </c>
@@ -2955,7 +2344,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>75</v>
       </c>
@@ -2966,7 +2355,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>76</v>
       </c>
@@ -2977,7 +2366,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>77</v>
       </c>
@@ -2988,7 +2377,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>82</v>
       </c>
@@ -2999,7 +2388,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>83</v>
       </c>
@@ -3010,7 +2399,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>84</v>
       </c>
@@ -3021,7 +2410,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>85</v>
       </c>
@@ -3032,7 +2421,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>86</v>
       </c>
@@ -3043,7 +2432,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>87</v>
       </c>
@@ -3054,7 +2443,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>88</v>
       </c>
@@ -3065,7 +2454,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>91</v>
       </c>
@@ -3076,7 +2465,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>93</v>
       </c>
@@ -3087,7 +2476,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>94</v>
       </c>
@@ -3098,7 +2487,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>48</v>
       </c>
@@ -3109,7 +2498,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>58</v>
       </c>
@@ -3120,7 +2509,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>68</v>
       </c>
@@ -3131,7 +2520,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>78</v>
       </c>
@@ -3142,9 +2531,9 @@
         <v>300</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
-      <c r="A155">
-        <v>79</v>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>84</v>
       </c>
       <c r="B155" t="s">
         <v>83</v>
@@ -3153,9 +2542,9 @@
         <v>300</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B156" t="s">
         <v>83</v>
@@ -3164,9 +2553,9 @@
         <v>300</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B157" t="s">
         <v>83</v>
@@ -3175,9 +2564,9 @@
         <v>300</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B158" t="s">
         <v>83</v>
@@ -3186,9 +2575,9 @@
         <v>300</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B159" t="s">
         <v>83</v>
@@ -3197,22 +2586,9 @@
         <v>300</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
-      <c r="A160" t="s">
-        <v>88</v>
-      </c>
-      <c r="B160" t="s">
-        <v>83</v>
-      </c>
-      <c r="C160">
-        <v>300</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B160" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:B159" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>